--- a/AAII_Financials/Quarterly/WSM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WSM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>WSM</t>
   </si>
@@ -656,546 +656,559 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E7" s="2">
         <v>46145</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46054</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45963</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45872</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45781</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45690</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45501</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45410</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45319</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45228</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45137</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44955</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44864</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44682</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44591</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44409</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44318</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44136</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44045</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43954</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43863</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43772</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43681</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43590</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43499</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43401</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43310</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43219</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43128</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43037</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42946</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42855</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42764</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1959800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1805500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2357100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1882800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1836800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1730100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2462200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1800700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1788300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1660300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2278900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1853700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1862600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1755500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2453100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2192600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2137500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1891200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2501000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2047500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1948300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1749000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2292700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1764500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1490800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1235200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1843600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1442500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1370800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1241100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1836400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1357000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1275200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1203000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1679900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1299300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1201600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1111500</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1581600</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1245400</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1068100</v>
+      </c>
+      <c r="E9" s="3">
         <v>1012000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1252200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1015100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>972100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>964300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1296600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>983100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>984400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>865200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1230300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1031300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1105000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1080400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1443200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1282000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1208700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1062700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1375800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1152100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1090000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>996200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1327400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1059000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>939600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>809600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1150900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>924300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>887000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>796800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1126500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>862000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>811200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>770800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1033700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>832300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>778900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>715700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>959600</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>787200</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>891600</v>
+      </c>
+      <c r="E10" s="3">
         <v>793400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1104900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>867700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>864600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>765800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1165600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>817600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>803900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>795200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1048600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>822400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>757600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>675100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1009900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>910600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>928800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>828500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1125200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>895400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>858300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>752800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>965300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>705500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>551200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>425600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>692700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>518200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>483800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>444300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>709900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>495000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>464000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>432200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>646200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>467000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>422700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>395800</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>622100</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>458200</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1238,8 +1251,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1360,8 +1374,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1482,58 +1499,61 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-116600</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3">
+        <v>300</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1600</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>-18900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1600</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>8300</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1550,21 +1570,21 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>5100</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>6400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>11400</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1574,83 +1594,86 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
         <v>7200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>6000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>6900</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>9100</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
       <c r="AM14" s="3">
         <v>0</v>
       </c>
       <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3">
         <v>5700</v>
       </c>
-      <c r="AO14" s="3">
-        <v>0</v>
-      </c>
       <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>56600</v>
+      </c>
+      <c r="E15" s="3">
         <v>56100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>60800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>57500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>56800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>56400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>58100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>58400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>56300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>57000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>66600</v>
-      </c>
-      <c r="N15" s="3">
-        <v>55200</v>
       </c>
       <c r="O15" s="3">
         <v>55200</v>
       </c>
       <c r="P15" s="3">
+        <v>55200</v>
+      </c>
+      <c r="Q15" s="3">
         <v>55600</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1726,8 +1749,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1767,252 +1793,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1621300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1513500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1878000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1563700</v>
       </c>
-      <c r="G17" s="3">
-        <v>1508700</v>
-      </c>
       <c r="H17" s="3">
+        <v>1508400</v>
+      </c>
+      <c r="I17" s="3">
         <v>1439400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1931100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1494000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1510400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1343200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1839700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1537000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1591100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1547700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1983300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1852900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1772000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1567700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1976500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1717300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1625200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1473900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1890600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1489900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1305400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1186600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1639900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1340600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1284600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1167000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1635600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1262600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1201000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1136500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1481000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1188500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1120000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1049000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1365800</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1135400</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>338500</v>
+      </c>
+      <c r="E18" s="3">
         <v>292000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>479100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>319100</v>
       </c>
-      <c r="G18" s="3">
-        <v>328100</v>
-      </c>
       <c r="H18" s="3">
+        <v>328400</v>
+      </c>
+      <c r="I18" s="3">
         <v>290700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>531100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>306600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>277900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>317100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>439200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>316700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>271500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>207800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>469800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>339700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>365500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>323500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>524500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>330200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>323100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>275100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>402100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>274600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>185400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>48600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>203700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>101900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>86200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>74100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>200800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>94400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>74200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>66600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>198900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>110800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>81600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>62500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>215800</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>110000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2055,8 +2088,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2099,208 +2133,214 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-600</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-100</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>395100</v>
+      </c>
+      <c r="E21" s="3">
         <v>348100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>539900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>376700</v>
       </c>
-      <c r="G21" s="3">
-        <v>384800</v>
-      </c>
       <c r="H21" s="3">
+        <v>385100</v>
+      </c>
+      <c r="I21" s="3">
         <v>347100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>589300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>365000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>334200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>374100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>505800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>371900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>326800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>263400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>527900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>395000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>418100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>373900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>574900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>379400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>371900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>321200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>448100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>316500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>225800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>92700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>249600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>146100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>130400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>118700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>246900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>139500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>118500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>113200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>246100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>155600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>126200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>107500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>261200</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>153900</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2343,8 +2383,8 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2421,252 +2461,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>461200</v>
+      </c>
+      <c r="E23" s="3">
         <v>298600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>486200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>328900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>337100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>300200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>542600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>316800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>293100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>333200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>471200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>322300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>274900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>205000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>471200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>340000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>365900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>323600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>524700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>330100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>323100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>273300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>399800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>269300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>178900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>46500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>202300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>99300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>83500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>71900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>199200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>92100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>72600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>65300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>198500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>110200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>81100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>62600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>215700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>109500</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E24" s="3">
         <v>67200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>118200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>87300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>89600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>69000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>131900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>79600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>76300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>72700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>116800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>85000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>73400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>48400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>116200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>88300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>98800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>69500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>121700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>80600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>77100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>45500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>90900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>67500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>44300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>11100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>36300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>24600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>20800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>19200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>42700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>25200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>20900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>17300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>61300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>38900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>28200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>23000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>71100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>40100</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2787,252 +2836,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>338100</v>
+      </c>
+      <c r="E26" s="3">
         <v>231400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>368000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>241600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>247600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>231300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>410700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>237300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>216900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>260400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>354400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>237300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>201500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>156500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>355000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>251700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>267100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>254100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>402900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>249500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>246100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>227800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>309000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>201800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>134600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>35400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>166000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>74700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>62600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>52700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>156500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>66900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>51700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>48000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>137300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>71300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>52900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>39600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>144600</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>338100</v>
+      </c>
+      <c r="E27" s="3">
         <v>231400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>368000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>241600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>247600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>231300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>410700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>237300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>216900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>260400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>354400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>237300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>201500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>156500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>355000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>251700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>267100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>254100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>402900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>249500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>246100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>227800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>309000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>201800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>134600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>35400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>166000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>74700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>62600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>52700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>156500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>66900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>51700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>48000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>137300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>71300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>52900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>39600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>144600</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3153,8 +3211,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3227,8 +3288,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3245,24 +3306,24 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>14600</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-2900</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-41500</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3275,8 +3336,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3397,8 +3461,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3519,8 +3586,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3563,208 +3633,214 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>-1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>5300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>6500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>600</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>100</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>338100</v>
+      </c>
+      <c r="E33" s="3">
         <v>231400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>368000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>241600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>247600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>231300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>410700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>237300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>216900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>260400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>354400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>237300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>201500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>156500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>355000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>251700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>267100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>254100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>402900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>249500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>246100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>227800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>309000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>201800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>134600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>35400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>166000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>74700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>62600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>52700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>155300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>81500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>51700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>45200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>95800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>71300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>52900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>39600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>144600</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3885,257 +3961,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>338100</v>
+      </c>
+      <c r="E35" s="3">
         <v>231400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>368000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>241600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>247600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>231300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>410700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>237300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>216900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>260400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>354400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>237300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>201500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>156500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>355000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>251700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>267100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>254100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>402900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>249500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>246100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>227800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>309000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>201800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>134600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>35400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>166000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>74700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>62600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>52700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>155300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>81500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>51700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>45200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>95800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>71300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>52900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>39600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>144600</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E38" s="2">
         <v>46145</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46054</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45963</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45872</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45781</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45690</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45501</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45410</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45319</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45228</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45137</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44955</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44864</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44682</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44591</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44409</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44318</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44136</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44045</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43954</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43863</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43772</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43681</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43590</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43499</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43401</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43310</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43219</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43128</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43037</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42946</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42855</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42764</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4178,8 +4263,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4222,130 +4308,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1028900</v>
+      </c>
+      <c r="E41" s="3">
         <v>651600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1019800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>884700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>985800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1047200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1213000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>826800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1265300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1254800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1262000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>698800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>514400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>297300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>367300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>113100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>124900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>324800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>850300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>656900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>655200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>639700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1200300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>773200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>947800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>861000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>432200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>155000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>120500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>107700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>339000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>164400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>174600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>290200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>390100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>90800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>103100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>94000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>213700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>75400</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4466,496 +4556,511 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>146200</v>
+      </c>
+      <c r="E43" s="3">
         <v>139300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>126800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>118400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>115500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>122800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>117700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>105600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>112500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>115200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>122900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>124200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>117000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>109200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>115700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>125800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>133500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>122900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>131700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>139500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>141800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>142500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>143700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>129800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>128700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>104800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>111700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>110100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>111100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>102200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>107100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>113600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>106300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>102600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>90100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>92300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>78700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>64000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>88800</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>96400</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1447400</v>
+      </c>
+      <c r="E44" s="3">
         <v>1455000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1462800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1530900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1433600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1335400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1332400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1450100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1247400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1218400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1246400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1396900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1300800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1401600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1456100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1687900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1542400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1396100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1246400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1272000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1170600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1087500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1006300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1125500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1042300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1070700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1100500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1258500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1187700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1155400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1125000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1197600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1099900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1052900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1061600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1176900</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1073000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1037100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>977500</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1063700</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E45" s="3">
         <v>19700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>23700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>20600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>20000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>22600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>24600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>19400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>19700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>22800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>29000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>27400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>26300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>28000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>96900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>133900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>127800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>84900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>95500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>108300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>106100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>79300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>116700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>108500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>136600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>112500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>111200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>135500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>138700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>120300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>123300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>115900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>96700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>77500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>106500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>100500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>109600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>96000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>87200</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>111700</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2746500</v>
+      </c>
+      <c r="E46" s="3">
         <v>2345700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2713200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2647000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2655500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2597300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2754600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2486800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2744300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2674000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2719800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2347300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2032100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1898800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2036100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2060700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1928700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1928900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2323900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2176700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2073700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1949000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2467100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2137000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2255400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2149000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1755600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1659200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1558000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1485600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1694300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1591400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1477500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1523200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1636400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1460500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1364400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1291000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1367200</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>1347200</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4998,8 +5103,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5076,130 +5181,136 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2444300</v>
+      </c>
+      <c r="E48" s="3">
         <v>2398100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2365400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2347700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2251300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2230400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2211700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2167500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2125300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2177900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2242800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2262200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2269300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2308600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2351800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2286200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2148000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2044500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2053500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2051500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1927900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1930100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1959900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1960700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2033600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2082600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2095400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2109800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2121600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2117000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>929600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>931400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>919700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>926300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>932300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>931100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>929300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>920500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>923300</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>918000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5216,7 +5327,7 @@
         <v>77400</v>
       </c>
       <c r="H49" s="3">
-        <v>77300</v>
+        <v>77400</v>
       </c>
       <c r="I49" s="3">
         <v>77300</v>
@@ -5246,16 +5357,16 @@
         <v>77300</v>
       </c>
       <c r="R49" s="3">
+        <v>77300</v>
+      </c>
+      <c r="S49" s="3">
         <v>85200</v>
-      </c>
-      <c r="S49" s="3">
-        <v>85300</v>
       </c>
       <c r="T49" s="3">
         <v>85300</v>
       </c>
       <c r="U49" s="3">
-        <v>85400</v>
+        <v>85300</v>
       </c>
       <c r="V49" s="3">
         <v>85400</v>
@@ -5276,38 +5387,38 @@
         <v>85400</v>
       </c>
       <c r="AB49" s="3">
-        <v>85300</v>
+        <v>85400</v>
       </c>
       <c r="AC49" s="3">
         <v>85300</v>
       </c>
       <c r="AD49" s="3">
+        <v>85300</v>
+      </c>
+      <c r="AE49" s="3">
         <v>85400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>85300</v>
-      </c>
-      <c r="AF49" s="3">
-        <v>85400</v>
       </c>
       <c r="AG49" s="3">
         <v>85400</v>
       </c>
       <c r="AH49" s="3">
+        <v>85400</v>
+      </c>
+      <c r="AI49" s="3">
         <v>85600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>85700</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK49" s="3">
+      <c r="AK49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL49" s="3">
         <v>18800</v>
       </c>
-      <c r="AL49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM49" s="3" t="s">
         <v>8</v>
       </c>
@@ -5320,8 +5431,11 @@
       <c r="AP49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5442,8 +5556,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5564,130 +5681,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>163600</v>
+      </c>
+      <c r="E52" s="3">
         <v>154700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>156700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>150800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>148400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>139900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>137300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>127300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>158700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>128600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>123000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>120600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>119400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>115500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>197800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>161900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>157200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>152000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>162800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>163700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>158000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>145700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>149000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>127600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>112800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>101100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>117600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>109400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>104700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>100400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>103500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>110300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>125100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>207400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>347900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>188800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>186200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>179600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>186400</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>188100</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5808,130 +5931,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5506300</v>
+      </c>
+      <c r="E54" s="3">
         <v>5059500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5411900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5311400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5228400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5157300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5301600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4968300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5211700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5160000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5273500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4883800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4571800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4471000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4663000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4594000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4319200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4210700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4625600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4477300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4245000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4110200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4661400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4310700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4487300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4418100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4054000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3963800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3869700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3788400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2812800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2718800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2608000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2656900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>2785700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2580400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>2479900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>2391200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>2476900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>2453300</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5974,8 +6103,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6018,175 +6148,179 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>703800</v>
+      </c>
+      <c r="E57" s="3">
         <v>560700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>638000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>667500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>601700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>553700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>645700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>665800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>595600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>502100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>607900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>675500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>597100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>629600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>508300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>720900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>680100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>642600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>612500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>638400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>601900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>574900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>543000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>562300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>373100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>423400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>521200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>444300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>404300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>385600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>526700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>487700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>466900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>393000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>457100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>470800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>429700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>399300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>453700</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>450100</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E58" s="3">
         <v>215200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>221400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>220200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>222600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>229100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>234200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>231700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>233400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>229600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>234500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>231200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>222200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>229800</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6209,350 +6343,359 @@
         <v>0</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>299400</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
       <c r="AA58" s="3">
-        <v>487800</v>
+        <v>0</v>
       </c>
       <c r="AB58" s="3">
         <v>487800</v>
       </c>
       <c r="AC58" s="3">
+        <v>487800</v>
+      </c>
+      <c r="AD58" s="3">
         <v>299800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>100000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>60000</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AH58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI58" s="3">
         <v>60000</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ58" s="3" t="s">
-        <v>8</v>
+      <c r="AJ58" s="3">
+        <v>0</v>
       </c>
       <c r="AK58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AL58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM58" s="3">
         <v>170000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>115000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>45000</v>
       </c>
-      <c r="AO58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AP58" s="3">
+      <c r="AP58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ58" s="3">
         <v>125000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>769900</v>
+      </c>
+      <c r="E59" s="3">
         <v>835500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>780200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>720700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>739200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>792400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>746100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>712700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>722200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>835200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>773600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>678300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>659600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>637300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1128100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1133900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1130900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1101000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1159200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1053300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>976900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>944400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1005700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>897800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>803300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>770900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>788500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>744600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>722500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>728600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>548100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>489000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>481000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>489800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>614000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>496800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>475400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>468300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>507500</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>455700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1898600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1762800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1954100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1855000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1766300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1721800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1912000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1845300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1758800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1721000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1880300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1789000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1663900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1701800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1636500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1854700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1811000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1743600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1771700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1691600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1578800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1519300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1848000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1460100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1664200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1682100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1609600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1288900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1186900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1114200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1074800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1036700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>947900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>882800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1007800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1137600</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1020100</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>912700</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>961300</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1030900</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1310900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1278400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1235500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1245500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1171700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1139700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1113100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1083800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1081100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1112300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1156100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1163600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1168200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1186200</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -6578,44 +6721,44 @@
         <v>0</v>
       </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>299200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>299000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>299900</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>299800</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>299700</v>
       </c>
       <c r="AF61" s="3">
         <v>299700</v>
       </c>
       <c r="AG61" s="3">
-        <v>299600</v>
+        <v>299700</v>
       </c>
       <c r="AH61" s="3">
         <v>299600</v>
       </c>
       <c r="AI61" s="3">
-        <v>299500</v>
+        <v>299600</v>
       </c>
       <c r="AJ61" s="3">
         <v>299500</v>
       </c>
       <c r="AK61" s="3">
+        <v>299500</v>
+      </c>
+      <c r="AL61" s="3">
         <v>299400</v>
       </c>
-      <c r="AL61" s="3">
-        <v>0</v>
-      </c>
       <c r="AM61" s="3">
         <v>0</v>
       </c>
@@ -6628,130 +6771,136 @@
       <c r="AP61" s="3">
         <v>0</v>
       </c>
+      <c r="AQ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>155900</v>
+      </c>
+      <c r="E62" s="3">
         <v>148600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>139700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>142900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>140700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>134500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>134100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>132600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>121500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>117100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>109300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>117900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>118800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>116200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1325500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1326400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1229900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1157300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1189700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1242300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1139500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1143700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1162200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1149500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1191200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1217200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1208600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1243300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1261500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1252700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>282700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>290500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>279500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>277400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>347700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>270700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>271300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>268400</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>267400</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>263000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6872,8 +7021,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6994,8 +7146,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7116,130 +7271,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3365400</v>
+      </c>
+      <c r="E66" s="3">
         <v>3189700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3329400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3243400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3078700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2996000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3159200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3061700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2961400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2950400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3145700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3070500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2950900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3004200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2962000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3181100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3040900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2901000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2961400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2934000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2718300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2662900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3010200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2908800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3154400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3199200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2818200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2831900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2748100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2666600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1657100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1626800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1527000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1459700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1582200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1408200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1291300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1181000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1228700</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>1293900</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7282,8 +7443,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7404,8 +7566,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7526,8 +7691,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7648,8 +7816,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7770,130 +7941,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1611600</v>
+      </c>
+      <c r="E72" s="3">
         <v>1364900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1509100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1517400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1622200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1654100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1591600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1377500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1728100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1704400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1555600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1260200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1084800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>951900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1141800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>877200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>750100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>789900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1074100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>963800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>964000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>894900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1019800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>792200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>736800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>641900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>644800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>550800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>552500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>564100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>584300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>532200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>528400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>638800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>647400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>623200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>640400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>671800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>701700</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>623200</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8014,8 +8191,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8136,8 +8316,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8258,130 +8441,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2140900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1869800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2082600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2068000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2149700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2161300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2142400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1906600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2250200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2209600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2127900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1813200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1621000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1466800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1701100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1412900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1278300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1309700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1664200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1543400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1526700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1447300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1651200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1401900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1332900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1218900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1235900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1131900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1121600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1121800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1155700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1091900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1081000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1197200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1203600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1172200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1188500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1210200</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>1248200</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>1159500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8502,257 +8691,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E80" s="2">
         <v>46145</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46054</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45963</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45872</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45781</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45690</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45501</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45410</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45319</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45228</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45137</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44955</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44864</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44682</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44591</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44409</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44318</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44136</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44045</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43954</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43863</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43772</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43681</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43590</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43499</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43401</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43310</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43219</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43128</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43037</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42946</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42855</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42764</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>338100</v>
+      </c>
+      <c r="E81" s="3">
         <v>231400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>368000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>241600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>247600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>231300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>410700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>237300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>216900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>260400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>354400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>237300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>201500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>156500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>355000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>251700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>267100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>254100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>402900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>249500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>246100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>227800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>309000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>201800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>134600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>35400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>166000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>74700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>62600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>52700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>155300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>81500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>51700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>45200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>95800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>71300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>52900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>39600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>144600</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8795,130 +8993,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E83" s="3">
         <v>56400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>58100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>58400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>56300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>57000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>66600</v>
-      </c>
-      <c r="J83" s="3">
-        <v>55200</v>
       </c>
       <c r="K83" s="3">
         <v>55200</v>
       </c>
       <c r="L83" s="3">
+        <v>55200</v>
+      </c>
+      <c r="M83" s="3">
         <v>55600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>56700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>55000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>52200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>50300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>56700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>55000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>52200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>50300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>50200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>49200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>48800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>47900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>48300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>47200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>46900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>46200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>47300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>46800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>46900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>46800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>47600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>47400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>45900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>47900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>47600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>45400</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>45100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>45000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>45500</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>44400</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9039,8 +9241,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9161,8 +9366,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9283,8 +9491,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9405,8 +9616,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9527,130 +9741,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>539500</v>
+      </c>
+      <c r="E89" s="3">
         <v>156300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>596900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>316300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>282700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>118900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>633500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>253500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>246500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>226800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>674900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>290400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>372500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>342500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>464300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>204900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>199100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>184500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>582800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>312700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>236800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>238900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>548200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>510200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>162500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>53900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>517300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>116600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>71400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-98100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>406500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>59400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>109400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>10800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>386800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>77800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>81500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-46400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>402200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>89000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9693,130 +9913,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-58700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-57700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-80900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-68200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-52000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-58300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-67200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-83400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-31400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-39500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-53600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-42000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-42900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-50000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-119700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-85800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-77400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-71200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-85500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-62700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-35900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-42400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-44600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-48800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-33800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-42300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-65100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-44000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-41000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-36100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-61800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-48300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-34000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-53900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-53100</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-50600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-32200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-70200</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-49300</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9937,8 +10161,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10059,130 +10286,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-58700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-57700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-80900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-68200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-53300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-58200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-67200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-83000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-31500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-39500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-53800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-41800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-42800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-49900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-119700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-85800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-77400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-71100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-85300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-62700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-35900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-42300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-44500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-48500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-33800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-42100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-64900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-44000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-40700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-36000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-61400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-47000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-45600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-33900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-134400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-52700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-50500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-32100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-70200</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-49300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10225,130 +10458,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>89900</v>
+      </c>
+      <c r="E96" s="3">
         <v>85600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>79900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>80600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>81300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>74700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>71200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>73100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>72900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>62900</v>
-      </c>
-      <c r="M96" s="3">
-        <v>57900</v>
       </c>
       <c r="N96" s="3">
         <v>57900</v>
       </c>
       <c r="O96" s="3">
+        <v>57900</v>
+      </c>
+      <c r="P96" s="3">
         <v>58600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>58100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-52100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-52600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-54500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-58200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-52300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-44100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-45500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-45600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-40900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-37500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-39900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-39400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-37500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-37700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-38600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-36900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-34700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-35300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-36300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-34100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-33100</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-33700</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-34000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-34200</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-32700</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-33300</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10469,8 +10706,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10591,8 +10831,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10713,370 +10956,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-103000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-467000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-382200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-349000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-291100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-230000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-177200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-608800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-204600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-193700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-59600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-62100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-114200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-362400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-92000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-128300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-320600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-637700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-300800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-248500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-183100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-759600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-83000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-637900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-41600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>419500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-174700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-39000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-17300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-96100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-170300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-22300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-178300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-79200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>49400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-40400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-19400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-41300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-194600</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-74100</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>3500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>6500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>2500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>3000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>100</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>800</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>377300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-368200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>135100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-101200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-61400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-165800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>386200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-438500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>563200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>184400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>217100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-70100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>254300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-11900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-199900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-525500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>193400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>15500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-560700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>427200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-174600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>86800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>428800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>277100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>34600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>12800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-231300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>174500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-10200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-115700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-99900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>299400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-12300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>9100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-119700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>138300</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-35700</v>
       </c>
     </row>
